--- a/セリフ編集/その他セリフ/関係性フラグ.xlsx
+++ b/セリフ編集/その他セリフ/関係性フラグ.xlsx
@@ -9394,7 +9394,7 @@
       </c>
       <c r="H248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……すまない。</t>
+          <t xml:space="preserve">……ごめん。</t>
         </is>
       </c>
     </row>
@@ -13686,7 +13686,7 @@
       </c>
       <c r="H364" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name2}、いい気にならないでね。次はわたしの番よ。</t>
+          <t xml:space="preserve">{name2}、いい気にならないでね。次は私の番よ。</t>
         </is>
       </c>
     </row>
@@ -13723,7 +13723,7 @@
       </c>
       <c r="H365" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一度や二度の番狂わせで、わたしを計らないで。</t>
+          <t xml:space="preserve">一度や二度の番狂わせで、私を計らないで。</t>
         </is>
       </c>
     </row>
